--- a/Team-Data/2008-09/2-24-2008-09.xlsx
+++ b/Team-Data/2008-09/2-24-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -754,7 +821,7 @@
         <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
@@ -769,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
         <v>18</v>
@@ -796,7 +863,7 @@
         <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
         <v>19</v>
@@ -808,7 +875,7 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0.789</v>
+        <v>0.793</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J3" t="n">
-        <v>77.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.486</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
         <v>16.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.392</v>
+        <v>0.389</v>
       </c>
       <c r="O3" t="n">
         <v>20.2</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.776</v>
+        <v>0.773</v>
       </c>
       <c r="R3" t="n">
         <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.8</v>
@@ -903,28 +970,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.9</v>
+        <v>101.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>3</v>
@@ -957,10 +1024,10 @@
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
         <v>18</v>
@@ -969,7 +1036,7 @@
         <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
@@ -981,16 +1048,16 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -1025,46 +1092,46 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" t="n">
         <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>0.386</v>
+        <v>0.393</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="J4" t="n">
-        <v>76.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="K4" t="n">
         <v>0.447</v>
       </c>
       <c r="L4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M4" t="n">
         <v>15.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.363</v>
+        <v>0.361</v>
       </c>
       <c r="O4" t="n">
         <v>17.9</v>
       </c>
       <c r="P4" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.738</v>
+        <v>0.739</v>
       </c>
       <c r="R4" t="n">
         <v>10.8</v>
@@ -1082,7 +1149,7 @@
         <v>15.6</v>
       </c>
       <c r="W4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X4" t="n">
         <v>4.8</v>
@@ -1091,28 +1158,28 @@
         <v>6.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>92.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
         <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
         <v>2</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
@@ -1133,13 +1200,13 @@
         <v>23</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
         <v>24</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
         <v>28</v>
@@ -1148,7 +1215,7 @@
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="n">
         <v>25</v>
@@ -1160,10 +1227,10 @@
         <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -1222,52 +1289,52 @@
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L5" t="n">
         <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O5" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="P5" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.792</v>
+        <v>0.789</v>
       </c>
       <c r="R5" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V5" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y5" t="n">
         <v>5.6</v>
@@ -1276,22 +1343,22 @@
         <v>21.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.8</v>
+        <v>100.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
         <v>18</v>
@@ -1306,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL5" t="n">
         <v>22</v>
@@ -1321,7 +1388,7 @@
         <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1339,13 +1406,13 @@
         <v>12</v>
       </c>
       <c r="AV5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
         <v>28</v>
@@ -1354,10 +1421,10 @@
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC5" t="n">
         <v>18</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -1392,46 +1459,46 @@
         <v>54</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J6" t="n">
-        <v>78.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K6" t="n">
         <v>0.474</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.389</v>
+        <v>0.386</v>
       </c>
       <c r="O6" t="n">
         <v>18.6</v>
       </c>
       <c r="P6" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.754</v>
+        <v>0.752</v>
       </c>
       <c r="R6" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S6" t="n">
         <v>31.1</v>
@@ -1440,40 +1507,40 @@
         <v>41.8</v>
       </c>
       <c r="U6" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>13</v>
+      </c>
+      <c r="W6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Z6" t="n">
         <v>20.3</v>
       </c>
-      <c r="V6" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>20.1</v>
-      </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.1</v>
+        <v>100.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
         <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
         <v>2</v>
@@ -1491,25 +1558,25 @@
         <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
         <v>4</v>
       </c>
       <c r="AN6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1518,28 +1585,28 @@
         <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV6" t="n">
         <v>5</v>
       </c>
       <c r="AW6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -1571,46 +1638,46 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" t="n">
         <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>0.589</v>
+        <v>0.6</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="J7" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K7" t="n">
-        <v>0.459</v>
+        <v>0.461</v>
       </c>
       <c r="L7" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M7" t="n">
         <v>19.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0.348</v>
+        <v>0.351</v>
       </c>
       <c r="O7" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P7" t="n">
         <v>21.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>11</v>
@@ -1619,19 +1686,19 @@
         <v>31.7</v>
       </c>
       <c r="T7" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U7" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="V7" t="n">
         <v>13.3</v>
       </c>
       <c r="W7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y7" t="n">
         <v>4.1</v>
@@ -1643,34 +1710,34 @@
         <v>19.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.6</v>
+        <v>101.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ7" t="n">
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>13</v>
@@ -1679,7 +1746,7 @@
         <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
         <v>25</v>
@@ -1691,7 +1758,7 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS7" t="n">
         <v>8</v>
@@ -1700,7 +1767,7 @@
         <v>8</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
@@ -1718,10 +1785,10 @@
         <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -1831,10 +1898,10 @@
         <v>2.6</v>
       </c>
       <c r="AD8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE8" t="n">
         <v>5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>6</v>
       </c>
       <c r="AF8" t="n">
         <v>6</v>
@@ -1846,16 +1913,16 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM8" t="n">
         <v>18</v>
@@ -1879,7 +1946,7 @@
         <v>13</v>
       </c>
       <c r="AT8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E9" t="n">
         <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>0.491</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1953,7 +2020,7 @@
         <v>35.9</v>
       </c>
       <c r="J9" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K9" t="n">
         <v>0.453</v>
@@ -1962,16 +2029,16 @@
         <v>4.6</v>
       </c>
       <c r="M9" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.342</v>
+        <v>0.345</v>
       </c>
       <c r="O9" t="n">
         <v>16.7</v>
       </c>
       <c r="P9" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0.744</v>
@@ -1980,16 +2047,16 @@
         <v>10.9</v>
       </c>
       <c r="S9" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T9" t="n">
-        <v>40.7</v>
+        <v>40.9</v>
       </c>
       <c r="U9" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V9" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="W9" t="n">
         <v>6.3</v>
@@ -1998,22 +2065,22 @@
         <v>4.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
         <v>16</v>
@@ -2028,7 +2095,7 @@
         <v>12</v>
       </c>
       <c r="AI9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
@@ -2037,13 +2104,13 @@
         <v>15</v>
       </c>
       <c r="AL9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM9" t="n">
         <v>28</v>
       </c>
       <c r="AN9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
         <v>29</v>
@@ -2061,10 +2128,10 @@
         <v>16</v>
       </c>
       <c r="AT9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2073,16 +2140,16 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY9" t="n">
         <v>6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2216,7 +2283,7 @@
         <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL10" t="n">
         <v>14</v>
@@ -2258,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
         <v>21</v>
       </c>
       <c r="G11" t="n">
-        <v>0.632</v>
+        <v>0.625</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2317,7 +2384,7 @@
         <v>35.5</v>
       </c>
       <c r="J11" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="K11" t="n">
         <v>0.446</v>
@@ -2326,25 +2393,25 @@
         <v>7.8</v>
       </c>
       <c r="M11" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0.38</v>
+        <v>0.379</v>
       </c>
       <c r="O11" t="n">
         <v>19.6</v>
       </c>
       <c r="P11" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S11" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T11" t="n">
         <v>43.1</v>
@@ -2356,28 +2423,28 @@
         <v>14.3</v>
       </c>
       <c r="W11" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X11" t="n">
         <v>3.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AA11" t="n">
         <v>20.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>3.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2389,7 +2456,7 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>26</v>
@@ -2401,7 +2468,7 @@
         <v>25</v>
       </c>
       <c r="AL11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM11" t="n">
         <v>6</v>
@@ -2413,10 +2480,10 @@
         <v>11</v>
       </c>
       <c r="AP11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR11" t="n">
         <v>17</v>
@@ -2425,10 +2492,10 @@
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV11" t="n">
         <v>14</v>
@@ -2446,7 +2513,7 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB11" t="n">
         <v>17</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2632,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG12" t="n">
         <v>21</v>
@@ -2580,10 +2647,10 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM12" t="n">
         <v>3</v>
@@ -2625,7 +2692,7 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
         <v>12</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-8.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -2765,13 +2832,13 @@
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
         <v>14</v>
       </c>
       <c r="AN13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
         <v>27</v>
@@ -2780,13 +2847,13 @@
         <v>23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR13" t="n">
         <v>11</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
         <v>22</v>
@@ -2798,7 +2865,7 @@
         <v>19</v>
       </c>
       <c r="AW13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2810,7 +2877,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -2860,70 +2927,70 @@
         <v>48.4</v>
       </c>
       <c r="I14" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="J14" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.479</v>
+        <v>0.478</v>
       </c>
       <c r="L14" t="n">
         <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.368</v>
+        <v>0.37</v>
       </c>
       <c r="O14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="P14" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R14" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S14" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T14" t="n">
-        <v>44.3</v>
+        <v>44.6</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V14" t="n">
         <v>13.6</v>
       </c>
       <c r="W14" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z14" t="n">
         <v>20.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB14" t="n">
-        <v>109.1</v>
+        <v>108.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2935,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2944,7 +3011,7 @@
         <v>4</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2968,7 +3035,7 @@
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2986,10 +3053,10 @@
         <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -3027,67 +3094,67 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>0.268</v>
+        <v>0.273</v>
       </c>
       <c r="H15" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="J15" t="n">
-        <v>77.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L15" t="n">
         <v>4.6</v>
       </c>
       <c r="M15" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
       <c r="O15" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="P15" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.752</v>
+        <v>0.754</v>
       </c>
       <c r="R15" t="n">
         <v>10.7</v>
       </c>
       <c r="S15" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="T15" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="U15" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W15" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y15" t="n">
         <v>5.3</v>
@@ -3096,16 +3163,16 @@
         <v>22.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.2</v>
+        <v>93.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.4</v>
+        <v>-6.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3126,10 +3193,10 @@
         <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM15" t="n">
         <v>27</v>
@@ -3141,16 +3208,16 @@
         <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT15" t="n">
         <v>26</v>
@@ -3159,16 +3226,16 @@
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX15" t="n">
         <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ15" t="n">
         <v>21</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F16" t="n">
         <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>0.536</v>
+        <v>0.527</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3227,37 +3294,37 @@
         <v>36.4</v>
       </c>
       <c r="J16" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L16" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M16" t="n">
         <v>19.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O16" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P16" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.749</v>
+        <v>0.747</v>
       </c>
       <c r="R16" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S16" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T16" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="U16" t="n">
         <v>19.8</v>
@@ -3269,25 +3336,25 @@
         <v>8.1</v>
       </c>
       <c r="X16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y16" t="n">
         <v>4</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA16" t="n">
         <v>19.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>96.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3308,7 +3375,7 @@
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
         <v>12</v>
@@ -3317,7 +3384,7 @@
         <v>10</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
         <v>28</v>
@@ -3326,13 +3393,13 @@
         <v>26</v>
       </c>
       <c r="AQ16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR16" t="n">
         <v>24</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AS16" t="n">
         <v>25</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>24</v>
       </c>
       <c r="AT16" t="n">
         <v>28</v>
@@ -3347,7 +3414,7 @@
         <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY16" t="n">
         <v>5</v>
@@ -3356,7 +3423,7 @@
         <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB16" t="n">
         <v>23</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
         <v>28</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
-        <v>0.483</v>
+        <v>0.475</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,7 +3476,7 @@
         <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K17" t="n">
         <v>0.45</v>
@@ -3418,34 +3485,34 @@
         <v>5.9</v>
       </c>
       <c r="M17" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O17" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="P17" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R17" t="n">
         <v>12.2</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
         <v>7.2</v>
@@ -3457,19 +3524,19 @@
         <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
         <v>23.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>15</v>
@@ -3499,10 +3566,10 @@
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP17" t="n">
         <v>7</v>
@@ -3517,7 +3584,7 @@
         <v>23</v>
       </c>
       <c r="AT17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU17" t="n">
         <v>10</v>
@@ -3532,10 +3599,10 @@
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -3573,34 +3640,34 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" t="n">
         <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>0.321</v>
+        <v>0.327</v>
       </c>
       <c r="H18" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J18" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L18" t="n">
         <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="N18" t="n">
         <v>0.345</v>
@@ -3609,22 +3676,22 @@
         <v>19.1</v>
       </c>
       <c r="P18" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R18" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S18" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T18" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U18" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V18" t="n">
         <v>14.5</v>
@@ -3636,28 +3703,28 @@
         <v>4.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Z18" t="n">
         <v>21.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.8</v>
+        <v>-3.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
       </c>
       <c r="AF18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG18" t="n">
         <v>25</v>
@@ -3696,13 +3763,13 @@
         <v>4</v>
       </c>
       <c r="AS18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT18" t="n">
         <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AV18" t="n">
         <v>16</v>
@@ -3720,7 +3787,7 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
         <v>15</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
@@ -3872,7 +3939,7 @@
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR19" t="n">
         <v>13</v>
@@ -3902,7 +3969,7 @@
         <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB19" t="n">
         <v>20</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>2.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
         <v>10</v>
@@ -4054,7 +4121,7 @@
         <v>22</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR20" t="n">
         <v>28</v>
@@ -4066,7 +4133,7 @@
         <v>29</v>
       </c>
       <c r="AU20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV20" t="n">
         <v>4</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
@@ -4209,7 +4276,7 @@
         <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4242,28 +4309,28 @@
         <v>14</v>
       </c>
       <c r="AS21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT21" t="n">
         <v>6</v>
       </c>
-      <c r="AT21" t="n">
-        <v>7</v>
-      </c>
       <c r="AU21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV21" t="n">
         <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" t="n">
         <v>13</v>
       </c>
       <c r="F22" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G22" t="n">
-        <v>0.228</v>
+        <v>0.232</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4322,7 +4389,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L22" t="n">
         <v>4.2</v>
@@ -4331,16 +4398,16 @@
         <v>11.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O22" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P22" t="n">
         <v>26.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.776</v>
+        <v>0.777</v>
       </c>
       <c r="R22" t="n">
         <v>12.3</v>
@@ -4361,10 +4428,10 @@
         <v>6.9</v>
       </c>
       <c r="X22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z22" t="n">
         <v>20.7</v>
@@ -4373,28 +4440,28 @@
         <v>20.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>98.2</v>
+        <v>98.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>-6.3</v>
+        <v>-6.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>28</v>
       </c>
       <c r="AF22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
@@ -4415,7 +4482,7 @@
         <v>8</v>
       </c>
       <c r="AP22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
         <v>11</v>
@@ -4430,7 +4497,7 @@
         <v>4</v>
       </c>
       <c r="AU22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4442,7 +4509,7 @@
         <v>21</v>
       </c>
       <c r="AY22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ22" t="n">
         <v>14</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -4483,25 +4550,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E23" t="n">
         <v>41</v>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
-        <v>0.732</v>
+        <v>0.745</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J23" t="n">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="K23" t="n">
         <v>0.459</v>
@@ -4513,13 +4580,13 @@
         <v>26.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.396</v>
+        <v>0.397</v>
       </c>
       <c r="O23" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="P23" t="n">
-        <v>27.3</v>
+        <v>27.5</v>
       </c>
       <c r="Q23" t="n">
         <v>0.72</v>
@@ -4528,10 +4595,10 @@
         <v>10.1</v>
       </c>
       <c r="S23" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="T23" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U23" t="n">
         <v>19.3</v>
@@ -4552,16 +4619,16 @@
         <v>20.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AB23" t="n">
         <v>102.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4576,13 +4643,13 @@
         <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4597,7 +4664,7 @@
         <v>10</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4621,13 +4688,13 @@
         <v>18</v>
       </c>
       <c r="AX23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>9</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>8</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>0.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE24" t="n">
         <v>16</v>
       </c>
       <c r="AF24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH24" t="n">
         <v>27</v>
@@ -4779,7 +4846,7 @@
         <v>16</v>
       </c>
       <c r="AP24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ24" t="n">
         <v>27</v>
@@ -4794,7 +4861,7 @@
         <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV24" t="n">
         <v>18</v>
@@ -4809,7 +4876,7 @@
         <v>16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA24" t="n">
         <v>11</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
         <v>24</v>
       </c>
       <c r="G25" t="n">
-        <v>0.571</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4865,19 +4932,19 @@
         <v>39.6</v>
       </c>
       <c r="J25" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K25" t="n">
         <v>0.501</v>
       </c>
       <c r="L25" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.388</v>
+        <v>0.386</v>
       </c>
       <c r="O25" t="n">
         <v>20.9</v>
@@ -4886,55 +4953,55 @@
         <v>27.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.763</v>
+        <v>0.76</v>
       </c>
       <c r="R25" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S25" t="n">
         <v>31.6</v>
       </c>
       <c r="T25" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U25" t="n">
         <v>22.5</v>
       </c>
       <c r="V25" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="W25" t="n">
         <v>6.7</v>
       </c>
       <c r="X25" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y25" t="n">
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>106.5</v>
+        <v>106.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF25" t="n">
         <v>12</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
         <v>23</v>
@@ -4943,31 +5010,31 @@
         <v>2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AM25" t="n">
         <v>20</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO25" t="n">
         <v>4</v>
       </c>
       <c r="AP25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AS25" t="n">
         <v>9</v>
@@ -4982,10 +5049,10 @@
         <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AY25" t="n">
         <v>8</v>
@@ -4994,7 +5061,7 @@
         <v>13</v>
       </c>
       <c r="BA25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB25" t="n">
         <v>3</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -5044,73 +5111,73 @@
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
         <v>79.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L26" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M26" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O26" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="P26" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R26" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="S26" t="n">
         <v>28.2</v>
       </c>
       <c r="T26" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U26" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V26" t="n">
         <v>13.1</v>
       </c>
       <c r="W26" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
         <v>6</v>
@@ -5119,16 +5186,16 @@
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5143,10 +5210,10 @@
         <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,31 +5222,31 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
         <v>17</v>
       </c>
       <c r="AV26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW26" t="n">
         <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY26" t="n">
         <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
         <v>14</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5371,7 @@
         <v>6</v>
       </c>
       <c r="AI27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="n">
         <v>12</v>
@@ -5322,10 +5389,10 @@
         <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
@@ -5352,7 +5419,7 @@
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
@@ -5361,7 +5428,7 @@
         <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E28" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F28" t="n">
         <v>17</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
@@ -5423,34 +5490,34 @@
         <v>20.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0.393</v>
+        <v>0.395</v>
       </c>
       <c r="O28" t="n">
         <v>15.7</v>
       </c>
       <c r="P28" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>32.2</v>
+        <v>32</v>
       </c>
       <c r="T28" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U28" t="n">
         <v>21.9</v>
       </c>
       <c r="V28" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="W28" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="X28" t="n">
         <v>4.3</v>
@@ -5459,19 +5526,19 @@
         <v>4.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA28" t="n">
         <v>18.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5492,10 +5559,10 @@
         <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM28" t="n">
         <v>8</v>
@@ -5519,7 +5586,7 @@
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F29" t="n">
         <v>36</v>
       </c>
       <c r="G29" t="n">
-        <v>0.39</v>
+        <v>0.379</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J29" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="K29" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L29" t="n">
         <v>6.1</v>
@@ -5611,13 +5678,13 @@
         <v>18.6</v>
       </c>
       <c r="P29" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.828</v>
+        <v>0.826</v>
       </c>
       <c r="R29" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S29" t="n">
         <v>30.5</v>
@@ -5626,10 +5693,10 @@
         <v>39.2</v>
       </c>
       <c r="U29" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="V29" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="W29" t="n">
         <v>6.2</v>
@@ -5647,13 +5714,13 @@
         <v>20.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.2</v>
+        <v>96.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.1</v>
+        <v>-3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>22</v>
@@ -5662,19 +5729,19 @@
         <v>23</v>
       </c>
       <c r="AG29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH29" t="n">
         <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL29" t="n">
         <v>21</v>
@@ -5686,7 +5753,7 @@
         <v>11</v>
       </c>
       <c r="AO29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP29" t="n">
         <v>27</v>
@@ -5704,16 +5771,16 @@
         <v>27</v>
       </c>
       <c r="AU29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY29" t="n">
         <v>9</v>
@@ -5722,7 +5789,7 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -5835,28 +5902,28 @@
         <v>3.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
         <v>9</v>
       </c>
       <c r="AF30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ30" t="n">
         <v>16</v>
       </c>
       <c r="AK30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5883,7 +5950,7 @@
         <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -5895,7 +5962,7 @@
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY30" t="n">
         <v>15</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6032,7 +6099,7 @@
         <v>29</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="n">
         <v>10</v>
@@ -6080,7 +6147,7 @@
         <v>26</v>
       </c>
       <c r="AY31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ31" t="n">
         <v>11</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-24-2008-09</t>
+          <t>2009-02-24</t>
         </is>
       </c>
     </row>
